--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N56_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N56_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>59.91848659973766</v>
+        <v>9.736754072457371</v>
       </c>
       <c r="D2" t="n">
-        <v>58.47359753019673</v>
+        <v>9.50195959865697</v>
       </c>
       <c r="E2" t="n">
-        <v>4.109700990661979</v>
+        <v>0.6678264109825716</v>
       </c>
       <c r="F2" t="n">
-        <v>5.952370028598867</v>
+        <v>0.9672601296473163</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>49.90368593735705</v>
+        <v>8.109348964820521</v>
       </c>
       <c r="D3" t="n">
-        <v>47.70191915829298</v>
+        <v>7.75156186322261</v>
       </c>
       <c r="E3" t="n">
-        <v>4.109700990661979</v>
+        <v>0.6678264109825716</v>
       </c>
       <c r="F3" t="n">
-        <v>5.952370028598867</v>
+        <v>0.9672601296473163</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>55.79495040771231</v>
+        <v>9.066679441253251</v>
       </c>
       <c r="D4" t="n">
-        <v>44.57797579136344</v>
+        <v>7.243921066096559</v>
       </c>
       <c r="E4" t="n">
-        <v>4.109700990661979</v>
+        <v>0.6678264109825716</v>
       </c>
       <c r="F4" t="n">
-        <v>5.952370028598867</v>
+        <v>0.9672601296473163</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
